--- a/Persistence/src/scripts/extracted/actors.actors_template.xlsx
+++ b/Persistence/src/scripts/extracted/actors.actors_template.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,30 +424,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>contact_person_id</t>
+          <t>sigep_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>treasury_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>initials</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>mission</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>vision</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
